--- a/Tableau de synthese.xlsx
+++ b/Tableau de synthese.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Tableau de synthèse Épreuve E4'!$A$1:$H$64</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Tableau de synthèse Épreuve E4'!$A$1:$H$62</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -607,13 +607,17 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -804,842 +808,912 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="70.42"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="18.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="9" style="0" width="11.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="9" style="2" width="11.43"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="44" style="1" width="10.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="2"/>
+      <c r="H1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="4" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" s="13" customFormat="true" ht="324.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="11" t="s">
+    <row r="6" s="14" customFormat="true" ht="324.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="13" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" s="13" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
+    <row r="7" s="14" customFormat="true" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-    </row>
-    <row r="8" s="13" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+    </row>
+    <row r="8" s="14" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="18" t="s">
+      <c r="B8" s="17"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
-    </row>
-    <row r="9" s="13" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="s">
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="20"/>
+    </row>
+    <row r="9" s="14" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18" t="s">
+      <c r="B9" s="17"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="19"/>
-    </row>
-    <row r="10" s="13" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="s">
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="20"/>
+    </row>
+    <row r="10" s="14" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18" t="s">
+      <c r="B10" s="17"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="19"/>
-    </row>
-    <row r="11" s="13" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="s">
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="20"/>
+    </row>
+    <row r="11" s="14" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18" t="s">
+      <c r="B11" s="17"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="18"/>
-      <c r="H11" s="19"/>
-    </row>
-    <row r="12" s="13" customFormat="true" ht="60" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="s">
+      <c r="G11" s="19"/>
+      <c r="H11" s="20"/>
+    </row>
+    <row r="12" s="14" customFormat="true" ht="60" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18" t="s">
+      <c r="B12" s="17"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="19"/>
-    </row>
-    <row r="13" s="13" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15" t="s">
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="20"/>
+    </row>
+    <row r="13" s="14" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18" t="s">
+      <c r="B13" s="17"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="G13" s="18"/>
-      <c r="H13" s="19"/>
-    </row>
-    <row r="14" s="13" customFormat="true" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15" t="s">
+      <c r="G13" s="19"/>
+      <c r="H13" s="20"/>
+    </row>
+    <row r="14" s="14" customFormat="true" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18" t="s">
+      <c r="B14" s="17"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="G14" s="18"/>
-      <c r="H14" s="19"/>
-    </row>
-    <row r="15" s="13" customFormat="true" ht="60" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="15" t="s">
+      <c r="G14" s="19"/>
+      <c r="H14" s="20"/>
+    </row>
+    <row r="15" s="14" customFormat="true" ht="60" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18" t="s">
+      <c r="B15" s="17"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18" t="s">
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="H15" s="19"/>
-    </row>
-    <row r="16" s="13" customFormat="true" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="15" t="s">
+      <c r="H15" s="20"/>
+    </row>
+    <row r="16" s="14" customFormat="true" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18" t="s">
+      <c r="B16" s="17"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="H16" s="19"/>
-    </row>
-    <row r="17" s="13" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15" t="s">
+      <c r="H16" s="20"/>
+    </row>
+    <row r="17" s="14" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="16"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="19" t="s">
+      <c r="B17" s="17"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="20" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="18" s="13" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="15"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="19"/>
-    </row>
-    <row r="19" s="13" customFormat="true" ht="75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="15" t="s">
+    <row r="18" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="16"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="20"/>
+    </row>
+    <row r="19" s="14" customFormat="true" ht="75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="16"/>
-      <c r="C19" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="19"/>
-    </row>
-    <row r="20" s="13" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="s">
+      <c r="B19" s="17"/>
+      <c r="C19" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="20"/>
+    </row>
+    <row r="20" s="14" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="16"/>
-      <c r="C20" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="19"/>
-    </row>
-    <row r="21" s="13" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="15" t="s">
+      <c r="B20" s="17"/>
+      <c r="C20" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="20"/>
+    </row>
+    <row r="21" s="14" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="19"/>
-    </row>
-    <row r="22" s="13" customFormat="true" ht="60" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15" t="s">
+      <c r="B21" s="17"/>
+      <c r="C21" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="20"/>
+    </row>
+    <row r="22" s="14" customFormat="true" ht="60" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="19"/>
-    </row>
-    <row r="23" s="13" customFormat="true" ht="60" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="15" t="s">
+      <c r="B22" s="17"/>
+      <c r="C22" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="20"/>
+    </row>
+    <row r="23" s="14" customFormat="true" ht="60" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="19"/>
-    </row>
-    <row r="24" s="13" customFormat="true" ht="60" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15" t="s">
+      <c r="B23" s="17"/>
+      <c r="C23" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="20"/>
+    </row>
+    <row r="24" s="14" customFormat="true" ht="60" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="19"/>
-    </row>
-    <row r="25" s="13" customFormat="true" ht="75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="15" t="s">
+      <c r="B24" s="17"/>
+      <c r="C24" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="20"/>
+    </row>
+    <row r="25" s="14" customFormat="true" ht="75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="19"/>
-    </row>
-    <row r="26" s="13" customFormat="true" ht="75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15" t="s">
+      <c r="B25" s="17"/>
+      <c r="C25" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="20"/>
+    </row>
+    <row r="26" s="14" customFormat="true" ht="75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="16"/>
-      <c r="C26" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="19"/>
-    </row>
-    <row r="27" s="13" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="19"/>
-    </row>
-    <row r="28" s="13" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="19"/>
-    </row>
-    <row r="29" s="13" customFormat="true" ht="60" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="s">
+      <c r="B26" s="17"/>
+      <c r="C26" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="20"/>
+    </row>
+    <row r="27" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="16"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="20"/>
+    </row>
+    <row r="28" s="14" customFormat="true" ht="60" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="B29" s="16"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="19"/>
-    </row>
-    <row r="30" s="13" customFormat="true" ht="60" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15" t="s">
+      <c r="B28" s="17"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="20"/>
+    </row>
+    <row r="29" s="14" customFormat="true" ht="60" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="16"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="19"/>
-    </row>
-    <row r="31" s="13" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15" t="s">
+      <c r="B29" s="17"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="20"/>
+    </row>
+    <row r="30" s="14" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B31" s="16"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="19"/>
-    </row>
-    <row r="32" s="13" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="15" t="s">
+      <c r="B30" s="17"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="20"/>
+    </row>
+    <row r="31" s="14" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B32" s="16"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="19"/>
-    </row>
-    <row r="33" s="13" customFormat="true" ht="60" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="15" t="s">
+      <c r="B31" s="17"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="20"/>
+    </row>
+    <row r="32" s="14" customFormat="true" ht="60" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B33" s="16"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="19"/>
-    </row>
-    <row r="34" s="13" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="15" t="s">
+      <c r="B32" s="17"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="20"/>
+    </row>
+    <row r="33" s="14" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B34" s="16"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="19"/>
-    </row>
-    <row r="35" s="13" customFormat="true" ht="90" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="15" t="s">
+      <c r="B33" s="17"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="20"/>
+    </row>
+    <row r="34" s="14" customFormat="true" ht="90" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B35" s="16"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="19"/>
-    </row>
-    <row r="36" s="13" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="15" t="s">
+      <c r="B34" s="17"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="20"/>
+    </row>
+    <row r="35" s="14" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B36" s="16"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="19"/>
-    </row>
-    <row r="37" s="13" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="15" t="s">
+      <c r="B35" s="17"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="20"/>
+    </row>
+    <row r="36" s="14" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B37" s="16"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="H37" s="19"/>
-    </row>
-    <row r="38" s="13" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="15" t="s">
+      <c r="B36" s="17"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="H36" s="20"/>
+    </row>
+    <row r="37" s="14" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="H38" s="19"/>
-    </row>
-    <row r="39" s="13" customFormat="true" ht="75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="15" t="s">
+      <c r="B37" s="17"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="H37" s="20"/>
+    </row>
+    <row r="38" s="14" customFormat="true" ht="75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B39" s="16"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="H39" s="19"/>
-    </row>
-    <row r="40" s="13" customFormat="true" ht="60" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="15" t="s">
+      <c r="B38" s="17"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="H38" s="20"/>
+    </row>
+    <row r="39" s="14" customFormat="true" ht="60" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="B40" s="16"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="H40" s="19"/>
-    </row>
-    <row r="41" s="13" customFormat="true" ht="60" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="15" t="s">
+      <c r="B39" s="17"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="H39" s="20"/>
+    </row>
+    <row r="40" s="14" customFormat="true" ht="60" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B41" s="16"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="H41" s="19"/>
-    </row>
-    <row r="42" s="13" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="15"/>
-      <c r="B42" s="16"/>
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="19"/>
-    </row>
-    <row r="43" s="13" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="15"/>
-      <c r="B43" s="16"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="19"/>
-    </row>
-    <row r="44" s="13" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="15" t="s">
+      <c r="B40" s="17"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="H40" s="20"/>
+    </row>
+    <row r="41" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="16"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="20"/>
+    </row>
+    <row r="42" s="14" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B44" s="16"/>
-      <c r="C44" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="H44" s="19"/>
-    </row>
-    <row r="45" s="13" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="15" t="s">
+      <c r="B42" s="17"/>
+      <c r="C42" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="H42" s="20"/>
+    </row>
+    <row r="43" s="14" customFormat="true" ht="45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="B45" s="16"/>
-      <c r="C45" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="H45" s="19"/>
-    </row>
-    <row r="46" s="13" customFormat="true" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="20" t="s">
+      <c r="B43" s="17"/>
+      <c r="C43" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="H43" s="20"/>
+    </row>
+    <row r="44" s="14" customFormat="true" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B46" s="20"/>
-      <c r="C46" s="20"/>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20"/>
-      <c r="F46" s="20"/>
-      <c r="G46" s="20"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="21"/>
+      <c r="H44" s="21"/>
+    </row>
+    <row r="45" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="16"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="20"/>
+    </row>
+    <row r="46" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="16"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="19"/>
       <c r="H46" s="20"/>
     </row>
-    <row r="47" s="13" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="15"/>
-      <c r="B47" s="16"/>
-      <c r="C47" s="18"/>
-      <c r="D47" s="18"/>
-      <c r="E47" s="18"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="19"/>
-    </row>
-    <row r="48" s="13" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="15"/>
-      <c r="B48" s="16"/>
-      <c r="C48" s="18"/>
-      <c r="D48" s="18"/>
-      <c r="E48" s="18"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
-      <c r="H48" s="19"/>
-    </row>
-    <row r="49" s="13" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="15"/>
-      <c r="B49" s="16"/>
-      <c r="C49" s="18"/>
-      <c r="D49" s="18"/>
-      <c r="E49" s="18"/>
-      <c r="F49" s="18"/>
-      <c r="G49" s="18"/>
-      <c r="H49" s="19"/>
-    </row>
-    <row r="50" s="13" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="15"/>
-      <c r="B50" s="16"/>
-      <c r="C50" s="18"/>
-      <c r="D50" s="18"/>
-      <c r="E50" s="18"/>
-      <c r="F50" s="18"/>
-      <c r="G50" s="18"/>
-      <c r="H50" s="19"/>
-    </row>
-    <row r="51" s="13" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="15"/>
-      <c r="B51" s="16"/>
-      <c r="C51" s="18"/>
-      <c r="D51" s="18"/>
-      <c r="E51" s="18"/>
-      <c r="F51" s="18"/>
-      <c r="G51" s="18"/>
-      <c r="H51" s="19"/>
-    </row>
-    <row r="52" s="13" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="15"/>
-      <c r="B52" s="16"/>
-      <c r="C52" s="18"/>
-      <c r="D52" s="18"/>
-      <c r="E52" s="18"/>
-      <c r="F52" s="18"/>
-      <c r="G52" s="18"/>
-      <c r="H52" s="19"/>
-    </row>
-    <row r="53" s="13" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="15"/>
-      <c r="B53" s="16"/>
-      <c r="C53" s="18"/>
-      <c r="D53" s="18"/>
-      <c r="E53" s="18"/>
-      <c r="F53" s="18"/>
-      <c r="G53" s="18"/>
-      <c r="H53" s="19"/>
-    </row>
-    <row r="54" s="13" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="15"/>
-      <c r="B54" s="16"/>
-      <c r="C54" s="18"/>
-      <c r="D54" s="18"/>
-      <c r="E54" s="18"/>
-      <c r="F54" s="18"/>
-      <c r="G54" s="18"/>
-      <c r="H54" s="19"/>
-    </row>
-    <row r="55" s="13" customFormat="true" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="20" t="s">
+    <row r="47" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="16"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="20"/>
+    </row>
+    <row r="48" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="16"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="19"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="20"/>
+    </row>
+    <row r="49" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="16"/>
+      <c r="B49" s="17"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="20"/>
+    </row>
+    <row r="50" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="16"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="19"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="19"/>
+      <c r="G50" s="19"/>
+      <c r="H50" s="20"/>
+    </row>
+    <row r="51" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="16"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
+      <c r="F51" s="19"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="20"/>
+    </row>
+    <row r="52" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="16"/>
+      <c r="B52" s="17"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="20"/>
+    </row>
+    <row r="53" s="14" customFormat="true" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="B55" s="20"/>
-      <c r="C55" s="20"/>
-      <c r="D55" s="20"/>
-      <c r="E55" s="20"/>
-      <c r="F55" s="20"/>
-      <c r="G55" s="20"/>
+      <c r="B53" s="21"/>
+      <c r="C53" s="21"/>
+      <c r="D53" s="21"/>
+      <c r="E53" s="21"/>
+      <c r="F53" s="21"/>
+      <c r="G53" s="21"/>
+      <c r="H53" s="21"/>
+    </row>
+    <row r="54" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="16"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="19"/>
+      <c r="H54" s="20"/>
+    </row>
+    <row r="55" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="16"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="19"/>
+      <c r="F55" s="19"/>
+      <c r="G55" s="19"/>
       <c r="H55" s="20"/>
     </row>
-    <row r="56" s="13" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="15"/>
-      <c r="B56" s="16"/>
-      <c r="C56" s="18"/>
-      <c r="D56" s="18"/>
-      <c r="E56" s="18"/>
-      <c r="F56" s="18"/>
-      <c r="G56" s="18"/>
-      <c r="H56" s="19"/>
-    </row>
-    <row r="57" s="13" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="15"/>
-      <c r="B57" s="16"/>
-      <c r="C57" s="18"/>
-      <c r="D57" s="18"/>
-      <c r="E57" s="18"/>
-      <c r="F57" s="18"/>
-      <c r="G57" s="18"/>
-      <c r="H57" s="19"/>
-    </row>
-    <row r="58" s="13" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="15"/>
-      <c r="B58" s="16"/>
-      <c r="C58" s="18"/>
-      <c r="D58" s="18"/>
-      <c r="E58" s="18"/>
-      <c r="F58" s="18"/>
-      <c r="G58" s="18"/>
-      <c r="H58" s="19"/>
-    </row>
-    <row r="59" s="13" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="15"/>
-      <c r="B59" s="16"/>
-      <c r="C59" s="18"/>
-      <c r="D59" s="18"/>
-      <c r="E59" s="18"/>
-      <c r="F59" s="18"/>
-      <c r="G59" s="18"/>
-      <c r="H59" s="19"/>
-    </row>
-    <row r="60" s="13" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="15"/>
-      <c r="B60" s="16"/>
-      <c r="C60" s="18"/>
-      <c r="D60" s="18"/>
-      <c r="E60" s="18"/>
-      <c r="F60" s="18"/>
-      <c r="G60" s="18"/>
-      <c r="H60" s="19"/>
-    </row>
-    <row r="61" s="13" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="15"/>
-      <c r="B61" s="16"/>
-      <c r="C61" s="18"/>
-      <c r="D61" s="18"/>
-      <c r="E61" s="18"/>
-      <c r="F61" s="18"/>
-      <c r="G61" s="18"/>
-      <c r="H61" s="19"/>
-    </row>
-    <row r="62" s="13" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="15"/>
-      <c r="B62" s="16"/>
-      <c r="C62" s="18"/>
-      <c r="D62" s="18"/>
-      <c r="E62" s="18"/>
-      <c r="F62" s="18"/>
-      <c r="G62" s="18"/>
-      <c r="H62" s="19"/>
-    </row>
-    <row r="63" s="13" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="21"/>
-      <c r="B63" s="22"/>
-      <c r="C63" s="23"/>
-      <c r="D63" s="23"/>
-      <c r="E63" s="23"/>
-      <c r="F63" s="23"/>
-      <c r="G63" s="23"/>
-      <c r="H63" s="24"/>
-    </row>
-    <row r="64" s="13" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="25"/>
-      <c r="B64" s="26"/>
-      <c r="C64" s="27"/>
-      <c r="D64" s="27"/>
-      <c r="E64" s="27"/>
-      <c r="F64" s="27"/>
-      <c r="G64" s="27"/>
-      <c r="H64" s="27"/>
-    </row>
-    <row r="65" s="13" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="16"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="19"/>
+      <c r="E56" s="19"/>
+      <c r="F56" s="19"/>
+      <c r="G56" s="19"/>
+      <c r="H56" s="20"/>
+    </row>
+    <row r="57" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="16"/>
+      <c r="B57" s="17"/>
+      <c r="C57" s="19"/>
+      <c r="D57" s="19"/>
+      <c r="E57" s="19"/>
+      <c r="F57" s="19"/>
+      <c r="G57" s="19"/>
+      <c r="H57" s="20"/>
+    </row>
+    <row r="58" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="16"/>
+      <c r="B58" s="17"/>
+      <c r="C58" s="19"/>
+      <c r="D58" s="19"/>
+      <c r="E58" s="19"/>
+      <c r="F58" s="19"/>
+      <c r="G58" s="19"/>
+      <c r="H58" s="20"/>
+    </row>
+    <row r="59" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="16"/>
+      <c r="B59" s="17"/>
+      <c r="C59" s="19"/>
+      <c r="D59" s="19"/>
+      <c r="E59" s="19"/>
+      <c r="F59" s="19"/>
+      <c r="G59" s="19"/>
+      <c r="H59" s="20"/>
+    </row>
+    <row r="60" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="16"/>
+      <c r="B60" s="17"/>
+      <c r="C60" s="19"/>
+      <c r="D60" s="19"/>
+      <c r="E60" s="19"/>
+      <c r="F60" s="19"/>
+      <c r="G60" s="19"/>
+      <c r="H60" s="20"/>
+    </row>
+    <row r="61" s="14" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="22"/>
+      <c r="B61" s="23"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="24"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="25"/>
+    </row>
+    <row r="62" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="26"/>
+      <c r="B62" s="27"/>
+      <c r="C62" s="28"/>
+      <c r="D62" s="28"/>
+      <c r="E62" s="28"/>
+      <c r="F62" s="28"/>
+      <c r="G62" s="28"/>
+      <c r="H62" s="28"/>
+    </row>
+    <row r="63" s="14" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
+      <c r="M63" s="2"/>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" s="2"/>
+      <c r="Q63" s="2"/>
+      <c r="R63" s="2"/>
+      <c r="S63" s="2"/>
+      <c r="T63" s="2"/>
+      <c r="U63" s="2"/>
+      <c r="V63" s="2"/>
+      <c r="W63" s="2"/>
+      <c r="X63" s="2"/>
+      <c r="Y63" s="2"/>
+      <c r="Z63" s="2"/>
+      <c r="AA63" s="2"/>
+      <c r="AB63" s="2"/>
+      <c r="AC63" s="2"/>
+      <c r="AD63" s="2"/>
+      <c r="AE63" s="2"/>
+      <c r="AF63" s="2"/>
+      <c r="AG63" s="2"/>
+      <c r="AH63" s="2"/>
+      <c r="AI63" s="2"/>
+      <c r="AJ63" s="2"/>
+      <c r="AK63" s="2"/>
+      <c r="AL63" s="2"/>
+      <c r="AM63" s="2"/>
+      <c r="AN63" s="2"/>
+      <c r="AO63" s="2"/>
+      <c r="AP63" s="2"/>
+      <c r="AQ63" s="2"/>
+    </row>
+    <row r="64" s="14" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="2"/>
+      <c r="L64" s="2"/>
+      <c r="M64" s="2"/>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" s="2"/>
+      <c r="Q64" s="2"/>
+      <c r="R64" s="2"/>
+      <c r="S64" s="2"/>
+      <c r="T64" s="2"/>
+      <c r="U64" s="2"/>
+      <c r="V64" s="2"/>
+      <c r="W64" s="2"/>
+      <c r="X64" s="2"/>
+      <c r="Y64" s="2"/>
+      <c r="Z64" s="2"/>
+      <c r="AA64" s="2"/>
+      <c r="AB64" s="2"/>
+      <c r="AC64" s="2"/>
+      <c r="AD64" s="2"/>
+      <c r="AE64" s="2"/>
+      <c r="AF64" s="2"/>
+      <c r="AG64" s="2"/>
+      <c r="AH64" s="2"/>
+      <c r="AI64" s="2"/>
+      <c r="AJ64" s="2"/>
+      <c r="AK64" s="2"/>
+      <c r="AL64" s="2"/>
+      <c r="AM64" s="2"/>
+      <c r="AN64" s="2"/>
+      <c r="AO64" s="2"/>
+      <c r="AP64" s="2"/>
+      <c r="AQ64" s="2"/>
+    </row>
+    <row r="65" s="14" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -1648,43 +1722,43 @@
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
-      <c r="I65" s="0"/>
-      <c r="J65" s="0"/>
-      <c r="K65" s="0"/>
-      <c r="L65" s="0"/>
-      <c r="M65" s="0"/>
-      <c r="N65" s="0"/>
-      <c r="O65" s="0"/>
-      <c r="P65" s="0"/>
-      <c r="Q65" s="0"/>
-      <c r="R65" s="0"/>
-      <c r="S65" s="0"/>
-      <c r="T65" s="0"/>
-      <c r="U65" s="0"/>
-      <c r="V65" s="0"/>
-      <c r="W65" s="0"/>
-      <c r="X65" s="0"/>
-      <c r="Y65" s="0"/>
-      <c r="Z65" s="0"/>
-      <c r="AA65" s="0"/>
-      <c r="AB65" s="0"/>
-      <c r="AC65" s="0"/>
-      <c r="AD65" s="0"/>
-      <c r="AE65" s="0"/>
-      <c r="AF65" s="0"/>
-      <c r="AG65" s="0"/>
-      <c r="AH65" s="0"/>
-      <c r="AI65" s="0"/>
-      <c r="AJ65" s="0"/>
-      <c r="AK65" s="0"/>
-      <c r="AL65" s="0"/>
-      <c r="AM65" s="0"/>
-      <c r="AN65" s="0"/>
-      <c r="AO65" s="0"/>
-      <c r="AP65" s="0"/>
-      <c r="AQ65" s="0"/>
-    </row>
-    <row r="66" s="13" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
+      <c r="L65" s="2"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" s="2"/>
+      <c r="Q65" s="2"/>
+      <c r="R65" s="2"/>
+      <c r="S65" s="2"/>
+      <c r="T65" s="2"/>
+      <c r="U65" s="2"/>
+      <c r="V65" s="2"/>
+      <c r="W65" s="2"/>
+      <c r="X65" s="2"/>
+      <c r="Y65" s="2"/>
+      <c r="Z65" s="2"/>
+      <c r="AA65" s="2"/>
+      <c r="AB65" s="2"/>
+      <c r="AC65" s="2"/>
+      <c r="AD65" s="2"/>
+      <c r="AE65" s="2"/>
+      <c r="AF65" s="2"/>
+      <c r="AG65" s="2"/>
+      <c r="AH65" s="2"/>
+      <c r="AI65" s="2"/>
+      <c r="AJ65" s="2"/>
+      <c r="AK65" s="2"/>
+      <c r="AL65" s="2"/>
+      <c r="AM65" s="2"/>
+      <c r="AN65" s="2"/>
+      <c r="AO65" s="2"/>
+      <c r="AP65" s="2"/>
+      <c r="AQ65" s="2"/>
+    </row>
+    <row r="66" s="14" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -1693,43 +1767,43 @@
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
-      <c r="I66" s="0"/>
-      <c r="J66" s="0"/>
-      <c r="K66" s="0"/>
-      <c r="L66" s="0"/>
-      <c r="M66" s="0"/>
-      <c r="N66" s="0"/>
-      <c r="O66" s="0"/>
-      <c r="P66" s="0"/>
-      <c r="Q66" s="0"/>
-      <c r="R66" s="0"/>
-      <c r="S66" s="0"/>
-      <c r="T66" s="0"/>
-      <c r="U66" s="0"/>
-      <c r="V66" s="0"/>
-      <c r="W66" s="0"/>
-      <c r="X66" s="0"/>
-      <c r="Y66" s="0"/>
-      <c r="Z66" s="0"/>
-      <c r="AA66" s="0"/>
-      <c r="AB66" s="0"/>
-      <c r="AC66" s="0"/>
-      <c r="AD66" s="0"/>
-      <c r="AE66" s="0"/>
-      <c r="AF66" s="0"/>
-      <c r="AG66" s="0"/>
-      <c r="AH66" s="0"/>
-      <c r="AI66" s="0"/>
-      <c r="AJ66" s="0"/>
-      <c r="AK66" s="0"/>
-      <c r="AL66" s="0"/>
-      <c r="AM66" s="0"/>
-      <c r="AN66" s="0"/>
-      <c r="AO66" s="0"/>
-      <c r="AP66" s="0"/>
-      <c r="AQ66" s="0"/>
-    </row>
-    <row r="67" s="13" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
+      <c r="L66" s="2"/>
+      <c r="M66" s="2"/>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" s="2"/>
+      <c r="Q66" s="2"/>
+      <c r="R66" s="2"/>
+      <c r="S66" s="2"/>
+      <c r="T66" s="2"/>
+      <c r="U66" s="2"/>
+      <c r="V66" s="2"/>
+      <c r="W66" s="2"/>
+      <c r="X66" s="2"/>
+      <c r="Y66" s="2"/>
+      <c r="Z66" s="2"/>
+      <c r="AA66" s="2"/>
+      <c r="AB66" s="2"/>
+      <c r="AC66" s="2"/>
+      <c r="AD66" s="2"/>
+      <c r="AE66" s="2"/>
+      <c r="AF66" s="2"/>
+      <c r="AG66" s="2"/>
+      <c r="AH66" s="2"/>
+      <c r="AI66" s="2"/>
+      <c r="AJ66" s="2"/>
+      <c r="AK66" s="2"/>
+      <c r="AL66" s="2"/>
+      <c r="AM66" s="2"/>
+      <c r="AN66" s="2"/>
+      <c r="AO66" s="2"/>
+      <c r="AP66" s="2"/>
+      <c r="AQ66" s="2"/>
+    </row>
+    <row r="67" s="14" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -1738,43 +1812,43 @@
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
-      <c r="I67" s="0"/>
-      <c r="J67" s="0"/>
-      <c r="K67" s="0"/>
-      <c r="L67" s="0"/>
-      <c r="M67" s="0"/>
-      <c r="N67" s="0"/>
-      <c r="O67" s="0"/>
-      <c r="P67" s="0"/>
-      <c r="Q67" s="0"/>
-      <c r="R67" s="0"/>
-      <c r="S67" s="0"/>
-      <c r="T67" s="0"/>
-      <c r="U67" s="0"/>
-      <c r="V67" s="0"/>
-      <c r="W67" s="0"/>
-      <c r="X67" s="0"/>
-      <c r="Y67" s="0"/>
-      <c r="Z67" s="0"/>
-      <c r="AA67" s="0"/>
-      <c r="AB67" s="0"/>
-      <c r="AC67" s="0"/>
-      <c r="AD67" s="0"/>
-      <c r="AE67" s="0"/>
-      <c r="AF67" s="0"/>
-      <c r="AG67" s="0"/>
-      <c r="AH67" s="0"/>
-      <c r="AI67" s="0"/>
-      <c r="AJ67" s="0"/>
-      <c r="AK67" s="0"/>
-      <c r="AL67" s="0"/>
-      <c r="AM67" s="0"/>
-      <c r="AN67" s="0"/>
-      <c r="AO67" s="0"/>
-      <c r="AP67" s="0"/>
-      <c r="AQ67" s="0"/>
-    </row>
-    <row r="68" s="13" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
+      <c r="L67" s="2"/>
+      <c r="M67" s="2"/>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" s="2"/>
+      <c r="Q67" s="2"/>
+      <c r="R67" s="2"/>
+      <c r="S67" s="2"/>
+      <c r="T67" s="2"/>
+      <c r="U67" s="2"/>
+      <c r="V67" s="2"/>
+      <c r="W67" s="2"/>
+      <c r="X67" s="2"/>
+      <c r="Y67" s="2"/>
+      <c r="Z67" s="2"/>
+      <c r="AA67" s="2"/>
+      <c r="AB67" s="2"/>
+      <c r="AC67" s="2"/>
+      <c r="AD67" s="2"/>
+      <c r="AE67" s="2"/>
+      <c r="AF67" s="2"/>
+      <c r="AG67" s="2"/>
+      <c r="AH67" s="2"/>
+      <c r="AI67" s="2"/>
+      <c r="AJ67" s="2"/>
+      <c r="AK67" s="2"/>
+      <c r="AL67" s="2"/>
+      <c r="AM67" s="2"/>
+      <c r="AN67" s="2"/>
+      <c r="AO67" s="2"/>
+      <c r="AP67" s="2"/>
+      <c r="AQ67" s="2"/>
+    </row>
+    <row r="68" s="14" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -1783,42 +1857,44 @@
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
-      <c r="I68" s="0"/>
-      <c r="J68" s="0"/>
-      <c r="K68" s="0"/>
-      <c r="L68" s="0"/>
-      <c r="M68" s="0"/>
-      <c r="N68" s="0"/>
-      <c r="O68" s="0"/>
-      <c r="P68" s="0"/>
-      <c r="Q68" s="0"/>
-      <c r="R68" s="0"/>
-      <c r="S68" s="0"/>
-      <c r="T68" s="0"/>
-      <c r="U68" s="0"/>
-      <c r="V68" s="0"/>
-      <c r="W68" s="0"/>
-      <c r="X68" s="0"/>
-      <c r="Y68" s="0"/>
-      <c r="Z68" s="0"/>
-      <c r="AA68" s="0"/>
-      <c r="AB68" s="0"/>
-      <c r="AC68" s="0"/>
-      <c r="AD68" s="0"/>
-      <c r="AE68" s="0"/>
-      <c r="AF68" s="0"/>
-      <c r="AG68" s="0"/>
-      <c r="AH68" s="0"/>
-      <c r="AI68" s="0"/>
-      <c r="AJ68" s="0"/>
-      <c r="AK68" s="0"/>
-      <c r="AL68" s="0"/>
-      <c r="AM68" s="0"/>
-      <c r="AN68" s="0"/>
-      <c r="AO68" s="0"/>
-      <c r="AP68" s="0"/>
-      <c r="AQ68" s="0"/>
-    </row>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" s="2"/>
+      <c r="Q68" s="2"/>
+      <c r="R68" s="2"/>
+      <c r="S68" s="2"/>
+      <c r="T68" s="2"/>
+      <c r="U68" s="2"/>
+      <c r="V68" s="2"/>
+      <c r="W68" s="2"/>
+      <c r="X68" s="2"/>
+      <c r="Y68" s="2"/>
+      <c r="Z68" s="2"/>
+      <c r="AA68" s="2"/>
+      <c r="AB68" s="2"/>
+      <c r="AC68" s="2"/>
+      <c r="AD68" s="2"/>
+      <c r="AE68" s="2"/>
+      <c r="AF68" s="2"/>
+      <c r="AG68" s="2"/>
+      <c r="AH68" s="2"/>
+      <c r="AI68" s="2"/>
+      <c r="AJ68" s="2"/>
+      <c r="AK68" s="2"/>
+      <c r="AL68" s="2"/>
+      <c r="AM68" s="2"/>
+      <c r="AN68" s="2"/>
+      <c r="AO68" s="2"/>
+      <c r="AP68" s="2"/>
+      <c r="AQ68" s="2"/>
+    </row>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -1834,8 +1910,8 @@
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A46:H46"/>
-    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A53:H53"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="true"/>
   <pageMargins left="0.196527777777778" right="0.196527777777778" top="0.196527777777778" bottom="0.196527777777778" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Tableau de synthese.xlsx
+++ b/Tableau de synthese.xlsx
@@ -804,7 +804,7 @@
   <sheetFormatPr defaultColWidth="10.71484375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="70.42"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="18.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="9" style="2" width="11.43"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="44" style="1" width="10.71"/>
